--- a/data/trans_orig/Q57-Clase-trans_orig.xlsx
+++ b/data/trans_orig/Q57-Clase-trans_orig.xlsx
@@ -513,7 +513,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Puntuación media de la autopercepción de felicidad</t>
+          <t>Puntuación media de la autopercepción de felicidad (tasa de respuesta: 99,48%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -631,27 +631,27 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>7,76; 8,05</t>
+          <t>7,78; 8,07</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>7,97; 8,26</t>
+          <t>7,99; 8,27</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>7,75; 8,05</t>
+          <t>7,73; 8,04</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>8,17; 8,41</t>
+          <t>8,18; 8,4</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>7,81; 8,02</t>
+          <t>7,81; 8,01</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -711,27 +711,27 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>7,75; 8,03</t>
+          <t>7,76; 8,03</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>8,13; 8,42</t>
+          <t>8,16; 8,43</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>7,59; 7,86</t>
+          <t>7,56; 7,84</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>8,01; 8,26</t>
+          <t>8,0; 8,25</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>7,71; 7,9</t>
+          <t>7,7; 7,89</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -791,32 +791,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>7,4; 7,68</t>
+          <t>7,39; 7,69</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>8,07; 8,79</t>
+          <t>8,07; 8,8</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>6,82; 7,41</t>
+          <t>6,86; 7,46</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>7,59; 8,0</t>
+          <t>7,61; 8,02</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>7,29; 7,57</t>
+          <t>7,3; 7,57</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>8,0; 8,7</t>
+          <t>8,0; 8,68</t>
         </is>
       </c>
     </row>
@@ -871,7 +871,7 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>7,55; 7,73</t>
+          <t>7,54; 7,72</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
@@ -881,17 +881,17 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>7,47; 7,7</t>
+          <t>7,48; 7,71</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>7,45; 8,12</t>
+          <t>7,48; 8,12</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>7,55; 7,7</t>
+          <t>7,54; 7,68</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
@@ -951,32 +951,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>7,19; 7,47</t>
+          <t>7,18; 7,46</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>7,71; 8,05</t>
+          <t>7,71; 8,07</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>6,97; 7,24</t>
+          <t>6,99; 7,24</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>7,4; 7,69</t>
+          <t>7,42; 7,69</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>7,11; 7,31</t>
+          <t>7,1; 7,29</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>7,54; 7,76</t>
+          <t>7,56; 7,77</t>
         </is>
       </c>
     </row>
@@ -1031,12 +1031,12 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>8,2; 8,47</t>
+          <t>8,19; 8,47</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>8,53; 8,99</t>
+          <t>8,53; 8,96</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
@@ -1046,17 +1046,17 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>7,66; 7,91</t>
+          <t>7,65; 7,9</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>7,49; 7,68</t>
+          <t>7,46; 7,68</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>7,91; 8,13</t>
+          <t>7,91; 8,15</t>
         </is>
       </c>
     </row>
@@ -1111,7 +1111,7 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>7,64; 7,74</t>
+          <t>7,63; 7,75</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
@@ -1121,17 +1121,17 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>7,39; 7,5</t>
+          <t>7,39; 7,51</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>7,68; 7,92</t>
+          <t>7,68; 7,93</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>7,52; 7,6</t>
+          <t>7,53; 7,6</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">

--- a/data/trans_orig/Q57-Clase-trans_orig.xlsx
+++ b/data/trans_orig/Q57-Clase-trans_orig.xlsx
@@ -608,7 +608,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>8,3</t>
+          <t>8,26</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -618,7 +618,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>8,21</t>
+          <t>8,2</t>
         </is>
       </c>
     </row>
@@ -631,7 +631,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>7,78; 8,07</t>
+          <t>7,79; 8,06</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -641,12 +641,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>7,73; 8,04</t>
+          <t>7,74; 8,05</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>8,18; 8,4</t>
+          <t>8,15; 8,37</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -656,7 +656,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>8,12; 8,3</t>
+          <t>8,1; 8,28</t>
         </is>
       </c>
     </row>
@@ -678,7 +678,7 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>8,29</t>
+          <t>8,3</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -698,7 +698,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>8,22</t>
+          <t>8,23</t>
         </is>
       </c>
     </row>
@@ -711,7 +711,7 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>7,76; 8,03</t>
+          <t>7,75; 8,03</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
@@ -721,7 +721,7 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>7,56; 7,84</t>
+          <t>7,59; 7,87</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -731,12 +731,12 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>7,7; 7,89</t>
+          <t>7,71; 7,9</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>8,12; 8,31</t>
+          <t>8,13; 8,31</t>
         </is>
       </c>
     </row>
@@ -758,7 +758,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>8,44</t>
+          <t>8,15</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -768,7 +768,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>7,82</t>
+          <t>7,85</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -778,7 +778,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>8,32</t>
+          <t>8,06</t>
         </is>
       </c>
     </row>
@@ -791,32 +791,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>7,39; 7,69</t>
+          <t>7,39; 7,68</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>8,07; 8,8</t>
+          <t>7,99; 8,29</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>6,86; 7,46</t>
+          <t>6,77; 7,46</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>7,61; 8,02</t>
+          <t>7,65; 8,04</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>7,3; 7,57</t>
+          <t>7,3; 7,58</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>8,0; 8,68</t>
+          <t>7,92; 8,19</t>
         </is>
       </c>
     </row>
@@ -838,7 +838,7 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>8,06</t>
+          <t>8,07</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -848,7 +848,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>7,86</t>
+          <t>8,08</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -858,7 +858,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>7,96</t>
+          <t>8,07</t>
         </is>
       </c>
     </row>
@@ -871,32 +871,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>7,54; 7,72</t>
+          <t>7,55; 7,73</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>7,95; 8,18</t>
+          <t>7,95; 8,17</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>7,48; 7,71</t>
+          <t>7,47; 7,7</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>7,48; 8,12</t>
+          <t>7,98; 8,16</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>7,54; 7,68</t>
+          <t>7,55; 7,69</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>7,66; 8,1</t>
+          <t>8,0; 8,14</t>
         </is>
       </c>
     </row>
@@ -918,7 +918,7 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>7,89</t>
+          <t>7,86</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -928,7 +928,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>7,55</t>
+          <t>7,47</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -938,7 +938,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>7,67</t>
+          <t>7,63</t>
         </is>
       </c>
     </row>
@@ -951,39 +951,39 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>7,18; 7,46</t>
+          <t>7,21; 7,47</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>7,71; 8,07</t>
+          <t>7,69; 8,0</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>6,99; 7,24</t>
+          <t>6,96; 7,24</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>7,42; 7,69</t>
+          <t>7,34; 7,58</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>7,1; 7,29</t>
+          <t>7,12; 7,31</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>7,56; 7,77</t>
+          <t>7,54; 7,73</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -998,7 +998,7 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>8,77</t>
+          <t>8,74</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -1008,7 +1008,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>7,78</t>
+          <t>7,8</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1018,7 +1018,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>8,02</t>
+          <t>8,01</t>
         </is>
       </c>
     </row>
@@ -1031,32 +1031,32 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>8,19; 8,47</t>
+          <t>8,21; 8,48</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>8,53; 8,96</t>
+          <t>8,5; 8,95</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>7,27; 7,5</t>
+          <t>7,26; 7,49</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>7,65; 7,9</t>
+          <t>7,69; 7,93</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>7,46; 7,68</t>
+          <t>7,48; 7,68</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>7,91; 8,15</t>
+          <t>7,9; 8,12</t>
         </is>
       </c>
     </row>
@@ -1078,7 +1078,7 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>8,21</t>
+          <t>8,14</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -1088,7 +1088,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>7,85</t>
+          <t>7,9</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1098,7 +1098,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>8,02</t>
+          <t>8,01</t>
         </is>
       </c>
     </row>
@@ -1111,12 +1111,12 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>7,63; 7,75</t>
+          <t>7,63; 7,74</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>8,12; 8,39</t>
+          <t>8,07; 8,19</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
@@ -1126,17 +1126,17 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>7,68; 7,93</t>
+          <t>7,85; 7,95</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>7,53; 7,6</t>
+          <t>7,52; 7,6</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>7,93; 8,13</t>
+          <t>7,97; 8,05</t>
         </is>
       </c>
     </row>
